--- a/hardware/mainboard/r141/pcbway/02_assembly/ENKU_R141_PCBWay_BOM_CPL_NO_FAB.xlsx
+++ b/hardware/mainboard/r141/pcbway/02_assembly/ENKU_R141_PCBWay_BOM_CPL_NO_FAB.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" r:id="R561bff17dd0a4b3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPL" sheetId="2" r:id="Rec36edf6854944f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" r:id="Rac48fd0da7da4967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPL" sheetId="2" r:id="R38d1ecbe41bd42a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -956,7 +956,7 @@
         <x:v>ENKU:ESP32_S3_WROOM_1_N16R8_EP_GRID_03_TENT_REQUEST</x:v>
       </x:c>
       <x:c r="G21" s="2" t="str">
-        <x:v>Hybrid</x:v>
+        <x:v>Surface mount</x:v>
       </x:c>
       <x:c r="H21" s="2" t="str">
         <x:v>Espressif</x:v>
@@ -2108,7 +2108,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16b183821dcc4294"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b5f0f97f0d14ad1"/>
 </x:worksheet>
 </file>
 
@@ -3961,6 +3961,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9cc75933df44fde"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb10dff970a4b460b"/>
 </x:worksheet>
 </file>